--- a/data/qa/prospect_to_cash/prospect.xlsx
+++ b/data/qa/prospect_to_cash/prospect.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0001</t>
+          <t>KB-0110</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Prospect Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Prospects</t>
-        </is>
-      </c>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is a Prospect?</t>
+          <t>What is a prospect in the Prospect Module and how is it managed?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A Prospect is a potential customer who has not yet been qualified as a Lead or Opportunity. It is the earliest stage in the Prospect-to-Cash process.</t>
+          <t>A prospect is a potential customer represented on the Prospects form. It can be associated with sales contacts, leads, opportunities, and estimates, and related interactions are displayed in separate read-only tabs. A prospect can later be moved to a customer, with related records reassigned and the old prospect record removed.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>prospect,potential customer</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>potential customer,lead contact</t>
-        </is>
-      </c>
+          <t>prospect, Prospects form, potential customer, related tabs</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>prospect.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Prospect Module &gt; Record meaning and forms</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,598 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0111</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>What happens to a prospect and its related records when it is moved to a customer?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>When a prospect is moved to a customer, related records are reassigned and the old prospect record is removed.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>prospect, customer, related records, reassigned</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Record meaning and forms</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0112</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I create and qualify a prospect?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>First, search Prospects and Customers to avoid a duplicate account. Then, create the company on Prospects and record the available organization, address, territory, and owner details. Create or select the person on Sales Contacts and use Prospect Sales Contact Cross References to connect that person to the prospect. Record calls and meetings in Sales Contact Interactions or Prospect Interactions, including the business need, next action, responsible owner, and follow-up date. Create a lead when there is a specific interest to pursue, and create an opportunity when the potential sale is qualified.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>create prospect, Sales Contacts, interactions, qualify</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Create and qualify a prospect</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0113</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>How do I move a prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>When the organization is ready to trade, use the Prospects form's Move To Customer action, review the Move Prospect To Customer form, provide any required bank code, process, and verify the new Customers record. Confirm the correct prospect and review linked leads, opportunities, estimates, and contacts afterward.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>move prospect to customer, convert prospect, customer creation</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Move prospect to customer</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0114</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What happens when I convert a prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Prospect conversion creates a customer and reassigns linked activity; verify the result. Because conversion changes record identity and relationships, confirm the correct prospect and review linked leads, opportunities, estimates, and contacts afterward.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>move prospect to customer, convert prospect, customer creation</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Move prospect to customer</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0115</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>What should I check if I can't find a prospect or contact in the system?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>If a prospect cannot be found, check the site, search criteria, and whether it has already been converted. If a contact is missing, inspect the sales contact cross-reference.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>missing prospect, missing contact, prospect converted, troubleshooting</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Common questions and checks</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0116</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Prospect Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>What should I do if a linked estimate or opportunity is missing from a read-only tab?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>If a linked estimate or opportunity is missing from a read-only tab, open the owning form and verify its prospect or customer reference.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>missing prospect, troubleshooting, estimate, opportunity</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>prospect.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Prospect Module &gt; Common questions and checks</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,36 +1248,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -696,7 +1286,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0001</t>
+          <t>KB-0110</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -706,7 +1296,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>define prospect</t>
+          <t>What does prospect mean in SyteLine?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -716,11 +1306,611 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0110</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>How are prospects handled before they become customers?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0110</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Can you explain what a prospect is and how it's managed?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0111</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>How are records handled when converting a prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0111</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What changes when a prospect becomes a customer?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0111</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Does the prospect record stay after conversion to customer?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0112</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to create and qualify a prospect?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0112</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I add a new prospect and move them to a lead or opportunity?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0112</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What's the process for qualifying a prospect in the system?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0113</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What are the steps to convert a prospect into a customer?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0113</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How can I change a prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0113</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What's the process for moving a prospect to customer status?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0114</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What does converting a prospect do?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0114</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>After moving a prospect to customer, what changes?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0114</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>What should I check after converting a prospect to a customer?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0115</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Why can't I find a prospect or contact?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0115</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What do I do if a prospect or contact is missing?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0115</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>How do I troubleshoot missing prospects or contacts?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0116</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How do I find a missing estimate or opportunity?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0116</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Why is my estimate or opportunity not showing up?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0116</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>What if an estimate or opportunity is missing from the tab?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
